--- a/EVE_Standard_Ore_Prices.xlsx
+++ b/EVE_Standard_Ore_Prices.xlsx
@@ -581,10 +581,10 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Pricing: average of ALL orders on each item page, IQR 1.5x outliers removed; BUY and SELL computed separately. Grade IV, Compressed, Batch Compressed excluded. N/A = no matching orders.</t>
+          <t>Pricing: for each ore, BEST SELL = lowest sell order, BEST BUY = highest buy order. Only orders within 1.5x of the corresponding BEST value are averaged (SELL: [BEST SELL, BEST SELL x1.5]; BUY: [BEST BUY / 1.5, BEST BUY]); orders deviating beyond 1.5x are excluded. BUY and SELL computed separately. Grade IV, Compressed and Batch Compressed excluded. N/A = no orders in range.</t>
         </is>
       </c>
     </row>
@@ -596,12 +596,12 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Acc SELL Price</t>
+          <t>Avg SELL Price</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>Acc BUY Price</t>
+          <t>Avg BUY Price</t>
         </is>
       </c>
     </row>
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5472.29</v>
+        <v>5633.09</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>2127.57</v>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3018</v>
+        <v>3526.33</v>
       </c>
     </row>
     <row r="9">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>2661.67</v>
+        <v>3580</v>
       </c>
     </row>
     <row r="11">
@@ -673,7 +673,7 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>10731.11</v>
+        <v>11158</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>6021.67</v>
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>3255</v>
+        <v>6500</v>
       </c>
     </row>
     <row r="14">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>6570</v>
+        <v>8140</v>
       </c>
     </row>
     <row r="16">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B17" s="8" t="n">
-        <v>41050</v>
+        <v>2416.67</v>
       </c>
       <c r="C17" s="8" t="n">
-        <v>1944.33</v>
+        <v>1880.86</v>
       </c>
     </row>
     <row r="18">
@@ -741,7 +741,7 @@
         <v>3605.5</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>1527</v>
+        <v>2303.5</v>
       </c>
     </row>
     <row r="19">
@@ -778,7 +778,7 @@
         <v>4665</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2826.66</v>
+        <v>4426.2</v>
       </c>
     </row>
     <row r="23">
@@ -793,7 +793,7 @@
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>2925.67</v>
+        <v>4388</v>
       </c>
     </row>
     <row r="24">
@@ -841,7 +841,7 @@
         <v>4004.5</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>2637.5</v>
+        <v>2682</v>
       </c>
     </row>
     <row r="29">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>4961.17</v>
+        <v>4907.12</v>
       </c>
       <c r="C37" s="8" t="n">
-        <v>820</v>
+        <v>1229.5</v>
       </c>
     </row>
     <row r="38">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>54.33</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43">
@@ -1037,7 +1037,7 @@
         </is>
       </c>
       <c r="B47" s="8" t="n">
-        <v>288.82</v>
+        <v>217.63</v>
       </c>
       <c r="C47" s="8" t="n">
         <v>41.5</v>
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B52" s="8" t="n">
-        <v>373.47</v>
+        <v>247.18</v>
       </c>
       <c r="C52" s="8" t="n">
-        <v>26.08</v>
+        <v>151.8</v>
       </c>
     </row>
     <row r="53">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>60.71</v>
+        <v>135</v>
       </c>
     </row>
     <row r="58">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="B62" s="8" t="n">
-        <v>2346.67</v>
+        <v>2335</v>
       </c>
       <c r="C62" s="8" t="n">
-        <v>1402.6</v>
+        <v>1477.17</v>
       </c>
     </row>
     <row r="63">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>1150</v>
+        <v>1724.5</v>
       </c>
     </row>
     <row r="66">
@@ -1264,7 +1264,7 @@
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>81.29000000000001</v>
+        <v>81.28</v>
       </c>
     </row>
     <row r="68">
@@ -1313,7 +1313,7 @@
         </is>
       </c>
       <c r="B72" s="8" t="n">
-        <v>3643</v>
+        <v>999.95</v>
       </c>
       <c r="C72" s="8" t="n">
         <v>506.45</v>
@@ -1331,7 +1331,7 @@
         </is>
       </c>
       <c r="C73" s="11" t="n">
-        <v>530.03</v>
+        <v>530.02</v>
       </c>
     </row>
     <row r="74">
@@ -1344,7 +1344,7 @@
         <v>1339.5</v>
       </c>
       <c r="C74" s="8" t="n">
-        <v>556.67</v>
+        <v>570</v>
       </c>
     </row>
     <row r="76">
@@ -1363,10 +1363,10 @@
         </is>
       </c>
       <c r="B77" s="8" t="n">
-        <v>1281.06</v>
+        <v>1160.58</v>
       </c>
       <c r="C77" s="8" t="n">
-        <v>916.04</v>
+        <v>923.16</v>
       </c>
     </row>
     <row r="78">
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>335.17</v>
+        <v>502.75</v>
       </c>
     </row>
     <row r="83">
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C83" s="11" t="n">
-        <v>392.9</v>
+        <v>589.35</v>
       </c>
     </row>
     <row r="84">
@@ -1448,7 +1448,7 @@
         </is>
       </c>
       <c r="C84" s="8" t="n">
-        <v>343.04</v>
+        <v>514.55</v>
       </c>
     </row>
     <row r="86">
@@ -1467,7 +1467,7 @@
         </is>
       </c>
       <c r="B87" s="8" t="n">
-        <v>2303.99</v>
+        <v>451.6</v>
       </c>
       <c r="C87" s="8" t="n">
         <v>233.34</v>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="B92" s="8" t="n">
-        <v>819.89</v>
+        <v>623.47</v>
       </c>
       <c r="C92" s="8" t="n">
-        <v>449.25</v>
+        <v>481.58</v>
       </c>
     </row>
     <row r="93">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="B93" s="11" t="n">
-        <v>387.37</v>
+        <v>158.95</v>
       </c>
       <c r="C93" s="11" t="n">
         <v>145.81</v>
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="B94" s="8" t="n">
-        <v>379.01</v>
+        <v>169</v>
       </c>
       <c r="C94" s="8" t="n">
         <v>144.57</v>
@@ -1644,7 +1644,7 @@
         <v>18995</v>
       </c>
       <c r="C104" s="8" t="n">
-        <v>10703.67</v>
+        <v>16055</v>
       </c>
     </row>
     <row r="106">
@@ -1666,7 +1666,7 @@
         <v>30</v>
       </c>
       <c r="C107" s="8" t="n">
-        <v>9.33</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="108">
@@ -1689,10 +1689,10 @@
         </is>
       </c>
       <c r="B109" s="8" t="n">
-        <v>41.7</v>
+        <v>17.53</v>
       </c>
       <c r="C109" s="8" t="n">
-        <v>11.35</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="111">
@@ -1716,7 +1716,7 @@
         </is>
       </c>
       <c r="C112" s="8" t="n">
-        <v>300.64</v>
+        <v>450.95</v>
       </c>
     </row>
     <row r="113">
@@ -1731,7 +1731,7 @@
         </is>
       </c>
       <c r="C113" s="11" t="n">
-        <v>302.64</v>
+        <v>453.95</v>
       </c>
     </row>
     <row r="114">
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="B117" s="8" t="n">
-        <v>384.16</v>
+        <v>121.7</v>
       </c>
       <c r="C117" s="8" t="n">
-        <v>36.46</v>
+        <v>97.03</v>
       </c>
     </row>
     <row r="118">
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="B118" s="11" t="n">
-        <v>128</v>
+        <v>124.18</v>
       </c>
       <c r="C118" s="11" t="n">
         <v>82.26000000000001</v>
@@ -1791,7 +1791,7 @@
         </is>
       </c>
       <c r="B119" s="8" t="n">
-        <v>133.66</v>
+        <v>120.07</v>
       </c>
       <c r="C119" s="8" t="n">
         <v>85.27</v>
@@ -1813,7 +1813,7 @@
         </is>
       </c>
       <c r="B122" s="8" t="n">
-        <v>49.13</v>
+        <v>33.84</v>
       </c>
       <c r="C122" s="8" t="n">
         <v>27.16</v>
@@ -1826,10 +1826,10 @@
         </is>
       </c>
       <c r="B123" s="11" t="n">
-        <v>40.36</v>
+        <v>39.41</v>
       </c>
       <c r="C123" s="11" t="n">
-        <v>26.94</v>
+        <v>27.63</v>
       </c>
     </row>
     <row r="124">
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="B124" s="8" t="n">
-        <v>57.23</v>
+        <v>35.8</v>
       </c>
       <c r="C124" s="8" t="n">
-        <v>28.06</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="126">
@@ -1864,7 +1864,7 @@
         <v>45153.33</v>
       </c>
       <c r="C127" s="8" t="n">
-        <v>9.17</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="128">
@@ -1917,10 +1917,10 @@
         </is>
       </c>
       <c r="B132" s="8" t="n">
-        <v>54.24</v>
+        <v>28.55</v>
       </c>
       <c r="C132" s="8" t="n">
-        <v>16.79</v>
+        <v>22.02</v>
       </c>
     </row>
     <row r="133">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="B133" s="11" t="n">
-        <v>25.99</v>
+        <v>25.98</v>
       </c>
       <c r="C133" s="11" t="n">
-        <v>16.06</v>
+        <v>21.58</v>
       </c>
     </row>
     <row r="134">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="B134" s="8" t="n">
-        <v>73.06999999999999</v>
+        <v>32.92</v>
       </c>
       <c r="C134" s="8" t="n">
-        <v>19.15</v>
+        <v>22.56</v>
       </c>
     </row>
     <row r="136">
@@ -1965,10 +1965,10 @@
         </is>
       </c>
       <c r="B137" s="8" t="n">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="C137" s="8" t="n">
-        <v>2500.01</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="138">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="C138" s="11" t="n">
-        <v>2500.01</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="139">
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="C139" s="8" t="n">
-        <v>2750.01</v>
+        <v>5500</v>
       </c>
     </row>
     <row r="141">
@@ -2017,7 +2017,7 @@
         </is>
       </c>
       <c r="B142" s="8" t="n">
-        <v>57.67</v>
+        <v>21.54</v>
       </c>
       <c r="C142" s="8" t="n">
         <v>14.78</v>
@@ -2030,7 +2030,7 @@
         </is>
       </c>
       <c r="B143" s="11" t="n">
-        <v>23.37</v>
+        <v>21.71</v>
       </c>
       <c r="C143" s="11" t="n">
         <v>16.72</v>
@@ -2043,7 +2043,7 @@
         </is>
       </c>
       <c r="B144" s="8" t="n">
-        <v>24.03</v>
+        <v>23.69</v>
       </c>
       <c r="C144" s="8" t="n">
         <v>15.94</v>
@@ -2065,10 +2065,10 @@
         </is>
       </c>
       <c r="B147" s="8" t="n">
-        <v>16577.5</v>
+        <v>15802.86</v>
       </c>
       <c r="C147" s="8" t="n">
-        <v>5311.75</v>
+        <v>7967</v>
       </c>
     </row>
     <row r="148">
@@ -2117,7 +2117,7 @@
         </is>
       </c>
       <c r="B152" s="8" t="n">
-        <v>13824.44</v>
+        <v>13430</v>
       </c>
       <c r="C152" s="8" t="n">
         <v>4759</v>
@@ -2133,7 +2133,7 @@
         <v>15000</v>
       </c>
       <c r="C153" s="11" t="n">
-        <v>3426.67</v>
+        <v>5140</v>
       </c>
     </row>
     <row r="154">
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="C154" s="8" t="n">
-        <v>3370.34</v>
+        <v>5055.5</v>
       </c>
     </row>
     <row r="156">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="B157" s="8" t="n">
-        <v>320</v>
+        <v>200</v>
       </c>
       <c r="C157" s="8" t="n">
         <v>4.51</v>
@@ -2226,7 +2226,7 @@
         <v>4500</v>
       </c>
       <c r="C162" s="8" t="n">
-        <v>335.5</v>
+        <v>503.25</v>
       </c>
     </row>
     <row r="163">
@@ -2254,7 +2254,7 @@
         </is>
       </c>
       <c r="C164" s="8" t="n">
-        <v>368.04</v>
+        <v>552.05</v>
       </c>
     </row>
     <row r="166">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B167" s="8" t="n">
-        <v>137.72</v>
+        <v>14.51</v>
       </c>
       <c r="C167" s="8" t="n">
         <v>10.14</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="B168" s="11" t="n">
-        <v>14.87</v>
+        <v>12.99</v>
       </c>
       <c r="C168" s="11" t="n">
         <v>10.65</v>
@@ -2299,7 +2299,7 @@
         </is>
       </c>
       <c r="B169" s="8" t="n">
-        <v>13.65</v>
+        <v>13.53</v>
       </c>
       <c r="C169" s="8" t="n">
         <v>10.44</v>
@@ -2321,7 +2321,7 @@
         </is>
       </c>
       <c r="B172" s="8" t="n">
-        <v>349.92</v>
+        <v>331.17</v>
       </c>
       <c r="C172" s="8" t="n">
         <v>249.78</v>
@@ -2339,7 +2339,7 @@
         </is>
       </c>
       <c r="C173" s="11" t="n">
-        <v>5536.67</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="174">
@@ -2354,7 +2354,7 @@
         </is>
       </c>
       <c r="C174" s="8" t="n">
-        <v>5603.33</v>
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/EVE_Standard_Ore_Prices.xlsx
+++ b/EVE_Standard_Ore_Prices.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +46,10 @@
       <b val="1"/>
       <color rgb="001F3864"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -110,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -118,28 +122,36 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -559,12 +571,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C174"/>
+  <dimension ref="A1:E174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="56" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -584,11 +598,11 @@
     <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Pricing: for each ore, BEST SELL = lowest sell order, BEST BUY = highest buy order. Only orders within 1.5x of the corresponding BEST value are averaged (SELL: [BEST SELL, BEST SELL x1.5]; BUY: [BEST BUY / 1.5, BEST BUY]); orders deviating beyond 1.5x are excluded. BUY and SELL computed separately. Grade IV, Compressed and Batch Compressed excluded. N/A = no orders in range.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
+          <t>Pricing: for each ore, BEST SELL = lowest sell order, BEST BUY = highest buy order. Only orders within 1.5x of the corresponding BEST value are averaged (SELL: [BEST SELL, BEST SELL x1.5]; BUY: [BEST BUY / 1.5, BEST BUY]); orders deviating beyond 1.5x are excluded. BUY and SELL computed separately. Grade IV, Compressed and Batch Compressed excluded. N/A = no orders in range. Volume and distribution columns are reference metadata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Grade</t>
@@ -604,8 +618,18 @@
           <t>Avg BUY Price</t>
         </is>
       </c>
-    </row>
-    <row r="6">
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Volume / unit</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Security / Distribution</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Arkonor</t>
@@ -613,51 +637,67 @@
       </c>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>Null-sec, Wormholes, Null anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
         <v>5633.09</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="10" t="n">
         <v>2127.57</v>
       </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="n">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="n">
         <v>3526.33</v>
       </c>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C9" s="8" t="n">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="n">
         <v>3580</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+    </row>
+    <row r="11" ht="30" customHeight="1">
       <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Bezdnacine</t>
@@ -665,51 +705,67 @@
       </c>
       <c r="B11" s="6" t="n"/>
       <c r="C11" s="6" t="n"/>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Pochven only</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
         <v>11158</v>
       </c>
-      <c r="C12" s="8" t="n">
+      <c r="C12" s="10" t="n">
         <v>6021.67</v>
       </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="n">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="n">
         <v>6500</v>
       </c>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="n">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="n">
         <v>8140</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Bistot</t>
@@ -717,49 +773,65 @@
       </c>
       <c r="B16" s="6" t="n"/>
       <c r="C16" s="6" t="n"/>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr">
+        <is>
+          <t>Null-sec, Wormholes, Null anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="n">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B17" s="10" t="n">
         <v>2416.67</v>
       </c>
-      <c r="C17" s="8" t="n">
+      <c r="C17" s="10" t="n">
         <v>1880.86</v>
       </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B18" s="11" t="n">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="n">
         <v>3605.5</v>
       </c>
-      <c r="C18" s="11" t="n">
+      <c r="C18" s="14" t="n">
         <v>2303.5</v>
       </c>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="n">
         <v>2001.17</v>
       </c>
-    </row>
-    <row r="21">
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+    </row>
+    <row r="21" ht="30" customHeight="1">
       <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Crokite</t>
@@ -767,49 +839,65 @@
       </c>
       <c r="B21" s="6" t="n"/>
       <c r="C21" s="6" t="n"/>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>Low-sec / Null-sec anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
         <v>4665</v>
       </c>
-      <c r="C22" s="8" t="n">
+      <c r="C22" s="10" t="n">
         <v>4426.2</v>
       </c>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="n">
         <v>4388</v>
       </c>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
         <v>4500</v>
       </c>
-      <c r="C24" s="8" t="n">
+      <c r="C24" s="10" t="n">
         <v>4432.67</v>
       </c>
-    </row>
-    <row r="26">
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Dark Ochre</t>
@@ -817,49 +905,65 @@
       </c>
       <c r="B26" s="6" t="n"/>
       <c r="C26" s="6" t="n"/>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>8 m³</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>Low-sec / Null-sec, Low/Null anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B27" s="10" t="n">
         <v>3718.5</v>
       </c>
-      <c r="C27" s="8" t="n">
+      <c r="C27" s="10" t="n">
         <v>2542.75</v>
       </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="n">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="n">
         <v>4004.5</v>
       </c>
-      <c r="C28" s="11" t="n">
+      <c r="C28" s="14" t="n">
         <v>2682</v>
       </c>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="n">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="n">
         <v>2833.75</v>
       </c>
-    </row>
-    <row r="31">
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Ducinium</t>
@@ -867,51 +971,67 @@
       </c>
       <c r="B31" s="6" t="n"/>
       <c r="C31" s="6" t="n"/>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>0.5 High/Low border, Null-sec &amp; Wormhole A0 systems</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="n">
         <v>4316.11</v>
       </c>
-      <c r="C32" s="8" t="n">
+      <c r="C32" s="10" t="n">
         <v>2582.33</v>
       </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B33" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B33" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="n">
         <v>1926.5</v>
       </c>
+      <c r="D33" s="15" t="n"/>
+      <c r="E33" s="15" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C34" s="8" t="n">
+      <c r="A34" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C34" s="10" t="n">
         <v>2405.5</v>
       </c>
-    </row>
-    <row r="36">
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Eifyrium</t>
@@ -919,51 +1039,67 @@
       </c>
       <c r="B36" s="6" t="n"/>
       <c r="C36" s="6" t="n"/>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>0.5 High/Low border, Null-sec &amp; Wormhole A0 systems</t>
+        </is>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="n">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
         <v>4907.12</v>
       </c>
-      <c r="C37" s="8" t="n">
+      <c r="C37" s="10" t="n">
         <v>1229.5</v>
       </c>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B38" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C38" s="11" t="n">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
         <v>1263.5</v>
       </c>
+      <c r="D38" s="15" t="n"/>
+      <c r="E38" s="15" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C39" s="8" t="n">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
         <v>1906.5</v>
       </c>
-    </row>
-    <row r="41">
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+    </row>
+    <row r="41" ht="30" customHeight="1">
       <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Kangite</t>
@@ -971,57 +1107,73 @@
       </c>
       <c r="B41" s="6" t="n"/>
       <c r="C41" s="6" t="n"/>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>0.1 m³</t>
+        </is>
+      </c>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>High-sec faction Bulwark</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C42" s="8" t="n">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n">
         <v>161</v>
       </c>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C43" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n"/>
+      <c r="E43" s="15" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+    </row>
+    <row r="46" ht="30" customHeight="1">
       <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Moissanite</t>
@@ -1029,55 +1181,71 @@
       </c>
       <c r="B46" s="6" t="n"/>
       <c r="C46" s="6" t="n"/>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>0.1 m³</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr">
+        <is>
+          <t>High-sec Gallente Bulwark</t>
+        </is>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B47" s="8" t="n">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="n">
         <v>217.63</v>
       </c>
-      <c r="C47" s="8" t="n">
+      <c r="C47" s="10" t="n">
         <v>41.5</v>
       </c>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B48" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C48" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A48" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="n"/>
+      <c r="E48" s="15" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B49" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C49" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
+      <c r="A49" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+    </row>
+    <row r="51" ht="30" customHeight="1">
       <c r="A51" s="5" t="inlineStr">
         <is>
           <t>Polycrase</t>
@@ -1085,55 +1253,71 @@
       </c>
       <c r="B51" s="6" t="n"/>
       <c r="C51" s="6" t="n"/>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>0.1 m³</t>
+        </is>
+      </c>
+      <c r="E51" s="8" t="inlineStr">
+        <is>
+          <t>High-sec Caldari Bulwark</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B52" s="8" t="n">
+      <c r="A52" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B52" s="10" t="n">
         <v>247.18</v>
       </c>
-      <c r="C52" s="8" t="n">
+      <c r="C52" s="10" t="n">
         <v>151.8</v>
       </c>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B53" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C53" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A53" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B53" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D53" s="15" t="n"/>
+      <c r="E53" s="15" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C54" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="n"/>
+      <c r="E54" s="11" t="n"/>
+    </row>
+    <row r="56" ht="30" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
           <t>Raspite</t>
@@ -1141,57 +1325,73 @@
       </c>
       <c r="B56" s="6" t="n"/>
       <c r="C56" s="6" t="n"/>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>0.1 m³</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>High-sec Amarr Bulwark</t>
+        </is>
+      </c>
     </row>
     <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B57" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C57" s="8" t="n">
+      <c r="A57" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C57" s="10" t="n">
         <v>135</v>
       </c>
+      <c r="D57" s="11" t="n"/>
+      <c r="E57" s="11" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B58" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C58" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B58" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D58" s="15" t="n"/>
+      <c r="E58" s="15" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C59" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
+      <c r="A59" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
+    </row>
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
           <t>Gneiss</t>
@@ -1199,51 +1399,67 @@
       </c>
       <c r="B61" s="6" t="n"/>
       <c r="C61" s="6" t="n"/>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>5 m³</t>
+        </is>
+      </c>
+      <c r="E61" s="8" t="inlineStr">
+        <is>
+          <t>Low-sec / Null-sec / Wormholes</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B62" s="8" t="n">
+      <c r="A62" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B62" s="10" t="n">
         <v>2335</v>
       </c>
-      <c r="C62" s="8" t="n">
+      <c r="C62" s="10" t="n">
         <v>1477.17</v>
       </c>
+      <c r="D62" s="11" t="n"/>
+      <c r="E62" s="11" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C63" s="11" t="n">
+      <c r="A63" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B63" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C63" s="14" t="n">
         <v>1616.33</v>
       </c>
+      <c r="D63" s="15" t="n"/>
+      <c r="E63" s="15" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B64" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C64" s="8" t="n">
+      <c r="A64" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C64" s="10" t="n">
         <v>1724.5</v>
       </c>
-    </row>
-    <row r="66">
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
+    </row>
+    <row r="66" ht="30" customHeight="1">
       <c r="A66" s="5" t="inlineStr">
         <is>
           <t>Griemeer</t>
@@ -1251,53 +1467,69 @@
       </c>
       <c r="B66" s="6" t="n"/>
       <c r="C66" s="6" t="n"/>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>0.8 m³</t>
+        </is>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>Null-sec Sov-Hub anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B67" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="n">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="n">
         <v>81.28</v>
       </c>
+      <c r="D67" s="11" t="n"/>
+      <c r="E67" s="11" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B68" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C68" s="11" t="n">
+      <c r="A68" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B68" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="n">
         <v>91.16</v>
       </c>
+      <c r="D68" s="15" t="n"/>
+      <c r="E68" s="15" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C69" s="8" t="n">
+      <c r="A69" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B69" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="n">
         <v>95.15000000000001</v>
       </c>
-    </row>
-    <row r="71">
+      <c r="D69" s="11" t="n"/>
+      <c r="E69" s="11" t="n"/>
+    </row>
+    <row r="71" ht="30" customHeight="1">
       <c r="A71" s="5" t="inlineStr">
         <is>
           <t>Hedbergite</t>
@@ -1305,49 +1537,65 @@
       </c>
       <c r="B71" s="6" t="n"/>
       <c r="C71" s="6" t="n"/>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>Low-sec / Low-sec anomalies / Wormholes</t>
+        </is>
+      </c>
     </row>
     <row r="72">
-      <c r="A72" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B72" s="8" t="n">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="n">
         <v>999.95</v>
       </c>
-      <c r="C72" s="8" t="n">
+      <c r="C72" s="10" t="n">
         <v>506.45</v>
       </c>
+      <c r="D72" s="11" t="n"/>
+      <c r="E72" s="11" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B73" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C73" s="11" t="n">
+      <c r="A73" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B73" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="n">
         <v>530.02</v>
       </c>
+      <c r="D73" s="15" t="n"/>
+      <c r="E73" s="15" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B74" s="8" t="n">
+      <c r="A74" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B74" s="10" t="n">
         <v>1339.5</v>
       </c>
-      <c r="C74" s="8" t="n">
+      <c r="C74" s="10" t="n">
         <v>570</v>
       </c>
-    </row>
-    <row r="76">
+      <c r="D74" s="11" t="n"/>
+      <c r="E74" s="11" t="n"/>
+    </row>
+    <row r="76" ht="30" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
           <t>Hemorphite</t>
@@ -1355,49 +1603,65 @@
       </c>
       <c r="B76" s="6" t="n"/>
       <c r="C76" s="6" t="n"/>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>3 m³</t>
+        </is>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>Low-sec / Low-sec anomalies / Wormholes</t>
+        </is>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B77" s="10" t="n">
         <v>1160.58</v>
       </c>
-      <c r="C77" s="8" t="n">
+      <c r="C77" s="10" t="n">
         <v>923.16</v>
       </c>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="11" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B78" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C78" s="11" t="n">
+      <c r="A78" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C78" s="14" t="n">
         <v>643.74</v>
       </c>
+      <c r="D78" s="15" t="n"/>
+      <c r="E78" s="15" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B79" s="8" t="n">
+      <c r="A79" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B79" s="10" t="n">
         <v>900</v>
       </c>
-      <c r="C79" s="8" t="n">
+      <c r="C79" s="10" t="n">
         <v>653.95</v>
       </c>
-    </row>
-    <row r="81">
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="11" t="n"/>
+    </row>
+    <row r="81" ht="30" customHeight="1">
       <c r="A81" s="5" t="inlineStr">
         <is>
           <t>Hezorime</t>
@@ -1405,53 +1669,69 @@
       </c>
       <c r="B81" s="6" t="n"/>
       <c r="C81" s="6" t="n"/>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>5 m³</t>
+        </is>
+      </c>
+      <c r="E81" s="8" t="inlineStr">
+        <is>
+          <t>Null-sec Sov-Hub anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B82" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="n">
+      <c r="A82" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B82" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C82" s="10" t="n">
         <v>502.75</v>
       </c>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B83" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C83" s="11" t="n">
+      <c r="A83" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B83" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C83" s="14" t="n">
         <v>589.35</v>
       </c>
+      <c r="D83" s="15" t="n"/>
+      <c r="E83" s="15" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="n">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B84" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C84" s="10" t="n">
         <v>514.55</v>
       </c>
-    </row>
-    <row r="86">
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
+    </row>
+    <row r="86" ht="30" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
           <t>Jaspet</t>
@@ -1459,47 +1739,63 @@
       </c>
       <c r="B86" s="6" t="n"/>
       <c r="C86" s="6" t="n"/>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>2 m³</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>Low-sec / Low-sec anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B87" s="8" t="n">
+      <c r="A87" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B87" s="10" t="n">
         <v>451.6</v>
       </c>
-      <c r="C87" s="8" t="n">
+      <c r="C87" s="10" t="n">
         <v>233.34</v>
       </c>
+      <c r="D87" s="11" t="n"/>
+      <c r="E87" s="11" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B88" s="11" t="n">
+      <c r="A88" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B88" s="14" t="n">
         <v>594</v>
       </c>
-      <c r="C88" s="11" t="n">
+      <c r="C88" s="14" t="n">
         <v>272.48</v>
       </c>
+      <c r="D88" s="15" t="n"/>
+      <c r="E88" s="15" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n">
+      <c r="A89" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B89" s="10" t="n">
         <v>626.67</v>
       </c>
-      <c r="C89" s="8" t="n">
+      <c r="C89" s="10" t="n">
         <v>276.83</v>
       </c>
-    </row>
-    <row r="91">
+      <c r="D89" s="11" t="n"/>
+      <c r="E89" s="11" t="n"/>
+    </row>
+    <row r="91" ht="30" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
           <t>Kernite</t>
@@ -1507,47 +1803,63 @@
       </c>
       <c r="B91" s="6" t="n"/>
       <c r="C91" s="6" t="n"/>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>1.2 m³</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>High-sec 0.5–0.8 anomalies; Low-sec / Null-sec / Wormholes</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="n">
+      <c r="A92" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B92" s="10" t="n">
         <v>623.47</v>
       </c>
-      <c r="C92" s="8" t="n">
+      <c r="C92" s="10" t="n">
         <v>481.58</v>
       </c>
+      <c r="D92" s="11" t="n"/>
+      <c r="E92" s="11" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="n">
+      <c r="A93" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B93" s="14" t="n">
         <v>158.95</v>
       </c>
-      <c r="C93" s="11" t="n">
+      <c r="C93" s="14" t="n">
         <v>145.81</v>
       </c>
+      <c r="D93" s="15" t="n"/>
+      <c r="E93" s="15" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B94" s="8" t="n">
+      <c r="A94" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B94" s="10" t="n">
         <v>169</v>
       </c>
-      <c r="C94" s="8" t="n">
+      <c r="C94" s="10" t="n">
         <v>144.57</v>
       </c>
-    </row>
-    <row r="96">
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="11" t="n"/>
+    </row>
+    <row r="96" ht="30" customHeight="1">
       <c r="A96" s="5" t="inlineStr">
         <is>
           <t>Kylixium</t>
@@ -1555,51 +1867,67 @@
       </c>
       <c r="B96" s="6" t="n"/>
       <c r="C96" s="6" t="n"/>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>1.2 m³</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Null-sec Sov-Hub anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="97">
-      <c r="A97" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B97" s="8" t="n">
+      <c r="A97" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B97" s="10" t="n">
         <v>263.2</v>
       </c>
-      <c r="C97" s="8" t="n">
+      <c r="C97" s="10" t="n">
         <v>238.43</v>
       </c>
+      <c r="D97" s="11" t="n"/>
+      <c r="E97" s="11" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B98" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C98" s="11" t="n">
+      <c r="A98" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B98" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C98" s="14" t="n">
         <v>216.6</v>
       </c>
+      <c r="D98" s="15" t="n"/>
+      <c r="E98" s="15" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B99" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="n">
+      <c r="A99" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B99" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="n">
         <v>200.85</v>
       </c>
-    </row>
-    <row r="101">
+      <c r="D99" s="11" t="n"/>
+      <c r="E99" s="11" t="n"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
       <c r="A101" s="5" t="inlineStr">
         <is>
           <t>Mercoxit</t>
@@ -1607,47 +1935,63 @@
       </c>
       <c r="B101" s="6" t="n"/>
       <c r="C101" s="6" t="n"/>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>40 m³</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Null-sec / Null anomalies; Pochven home systems</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B102" s="8" t="n">
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B102" s="10" t="n">
         <v>26454</v>
       </c>
-      <c r="C102" s="8" t="n">
+      <c r="C102" s="10" t="n">
         <v>14146</v>
       </c>
+      <c r="D102" s="11" t="n"/>
+      <c r="E102" s="11" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B103" s="11" t="n">
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B103" s="14" t="n">
         <v>25100</v>
       </c>
-      <c r="C103" s="11" t="n">
+      <c r="C103" s="14" t="n">
         <v>12056.67</v>
       </c>
+      <c r="D103" s="15" t="n"/>
+      <c r="E103" s="15" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B104" s="8" t="n">
+      <c r="A104" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B104" s="10" t="n">
         <v>18995</v>
       </c>
-      <c r="C104" s="8" t="n">
+      <c r="C104" s="10" t="n">
         <v>16055</v>
       </c>
-    </row>
-    <row r="106">
+      <c r="D104" s="11" t="n"/>
+      <c r="E104" s="11" t="n"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
           <t>Mordunium</t>
@@ -1655,47 +1999,63 @@
       </c>
       <c r="B106" s="6" t="n"/>
       <c r="C106" s="6" t="n"/>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>0.1 m³</t>
+        </is>
+      </c>
+      <c r="E106" s="8" t="inlineStr">
+        <is>
+          <t>High-sec 0.5 border systems; Low-sec; Null/W-space A0 systems</t>
+        </is>
+      </c>
     </row>
     <row r="107">
-      <c r="A107" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B107" s="8" t="n">
+      <c r="A107" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B107" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="C107" s="8" t="n">
+      <c r="C107" s="10" t="n">
         <v>17.01</v>
       </c>
+      <c r="D107" s="11" t="n"/>
+      <c r="E107" s="11" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B108" s="11" t="n">
+      <c r="A108" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B108" s="14" t="n">
         <v>21</v>
       </c>
-      <c r="C108" s="11" t="n">
+      <c r="C108" s="14" t="n">
         <v>10.36</v>
       </c>
+      <c r="D108" s="15" t="n"/>
+      <c r="E108" s="15" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="n">
+      <c r="A109" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="n">
         <v>17.53</v>
       </c>
-      <c r="C109" s="8" t="n">
+      <c r="C109" s="10" t="n">
         <v>11.01</v>
       </c>
-    </row>
-    <row r="111">
+      <c r="D109" s="11" t="n"/>
+      <c r="E109" s="11" t="n"/>
+    </row>
+    <row r="111" ht="30" customHeight="1">
       <c r="A111" s="5" t="inlineStr">
         <is>
           <t>Nocxite</t>
@@ -1703,53 +2063,69 @@
       </c>
       <c r="B111" s="6" t="n"/>
       <c r="C111" s="6" t="n"/>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>4 m³</t>
+        </is>
+      </c>
+      <c r="E111" s="8" t="inlineStr">
+        <is>
+          <t>Low-sec Prospecting Arrays / Null-sec Sov-Hub anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B112" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C112" s="8" t="n">
+      <c r="A112" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C112" s="10" t="n">
         <v>450.95</v>
       </c>
+      <c r="D112" s="11" t="n"/>
+      <c r="E112" s="11" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B113" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C113" s="11" t="n">
+      <c r="A113" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B113" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C113" s="14" t="n">
         <v>453.95</v>
       </c>
+      <c r="D113" s="15" t="n"/>
+      <c r="E113" s="15" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B114" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C114" s="8" t="n">
+      <c r="A114" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="n">
         <v>503.65</v>
       </c>
-    </row>
-    <row r="116">
+      <c r="D114" s="11" t="n"/>
+      <c r="E114" s="11" t="n"/>
+    </row>
+    <row r="116" ht="30" customHeight="1">
       <c r="A116" s="5" t="inlineStr">
         <is>
           <t>Omber</t>
@@ -1757,47 +2133,63 @@
       </c>
       <c r="B116" s="6" t="n"/>
       <c r="C116" s="6" t="n"/>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>0.6 m³</t>
+        </is>
+      </c>
+      <c r="E116" s="8" t="inlineStr">
+        <is>
+          <t>High-sec 0.5–0.8 anomalies; Low-sec / Null anomalies / Wormholes</t>
+        </is>
+      </c>
     </row>
     <row r="117">
-      <c r="A117" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B117" s="8" t="n">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B117" s="10" t="n">
         <v>121.7</v>
       </c>
-      <c r="C117" s="8" t="n">
+      <c r="C117" s="10" t="n">
         <v>97.03</v>
       </c>
+      <c r="D117" s="11" t="n"/>
+      <c r="E117" s="11" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B118" s="11" t="n">
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="n">
         <v>124.18</v>
       </c>
-      <c r="C118" s="11" t="n">
+      <c r="C118" s="14" t="n">
         <v>82.26000000000001</v>
       </c>
+      <c r="D118" s="15" t="n"/>
+      <c r="E118" s="15" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="n">
+      <c r="A119" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="n">
         <v>120.07</v>
       </c>
-      <c r="C119" s="8" t="n">
+      <c r="C119" s="10" t="n">
         <v>85.27</v>
       </c>
-    </row>
-    <row r="121">
+      <c r="D119" s="11" t="n"/>
+      <c r="E119" s="11" t="n"/>
+    </row>
+    <row r="121" ht="30" customHeight="1">
       <c r="A121" s="5" t="inlineStr">
         <is>
           <t>Plagioclase</t>
@@ -1805,47 +2197,63 @@
       </c>
       <c r="B121" s="6" t="n"/>
       <c r="C121" s="6" t="n"/>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>0.35 m³</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>High-sec / Low-sec / Wormholes</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B122" s="8" t="n">
+      <c r="A122" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B122" s="10" t="n">
         <v>33.84</v>
       </c>
-      <c r="C122" s="8" t="n">
+      <c r="C122" s="10" t="n">
         <v>27.16</v>
       </c>
+      <c r="D122" s="11" t="n"/>
+      <c r="E122" s="11" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B123" s="11" t="n">
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B123" s="14" t="n">
         <v>39.41</v>
       </c>
-      <c r="C123" s="11" t="n">
+      <c r="C123" s="14" t="n">
         <v>27.63</v>
       </c>
+      <c r="D123" s="15" t="n"/>
+      <c r="E123" s="15" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B124" s="8" t="n">
+      <c r="A124" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B124" s="10" t="n">
         <v>35.8</v>
       </c>
-      <c r="C124" s="8" t="n">
+      <c r="C124" s="10" t="n">
         <v>29.15</v>
       </c>
-    </row>
-    <row r="126">
+      <c r="D124" s="11" t="n"/>
+      <c r="E124" s="11" t="n"/>
+    </row>
+    <row r="126" ht="30" customHeight="1">
       <c r="A126" s="5" t="inlineStr">
         <is>
           <t>Prismaticite</t>
@@ -1853,55 +2261,71 @@
       </c>
       <c r="B126" s="6" t="n"/>
       <c r="C126" s="6" t="n"/>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>40 m³</t>
+        </is>
+      </c>
+      <c r="E126" s="8" t="inlineStr">
+        <is>
+          <t>Special/limited distribution</t>
+        </is>
+      </c>
     </row>
     <row r="127">
-      <c r="A127" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B127" s="8" t="n">
+      <c r="A127" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B127" s="10" t="n">
         <v>45153.33</v>
       </c>
-      <c r="C127" s="8" t="n">
+      <c r="C127" s="10" t="n">
         <v>2002</v>
       </c>
+      <c r="D127" s="11" t="n"/>
+      <c r="E127" s="11" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B128" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C128" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C128" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="n"/>
+      <c r="E128" s="15" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B129" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C129" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
+      <c r="A129" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B129" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C129" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D129" s="11" t="n"/>
+      <c r="E129" s="11" t="n"/>
+    </row>
+    <row r="131" ht="30" customHeight="1">
       <c r="A131" s="5" t="inlineStr">
         <is>
           <t>Pyroxeres</t>
@@ -1909,47 +2333,63 @@
       </c>
       <c r="B131" s="6" t="n"/>
       <c r="C131" s="6" t="n"/>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>0.3 m³</t>
+        </is>
+      </c>
+      <c r="E131" s="8" t="inlineStr">
+        <is>
+          <t>High-sec / Low-sec / Null anomalies / Wormholes</t>
+        </is>
+      </c>
     </row>
     <row r="132">
-      <c r="A132" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B132" s="8" t="n">
+      <c r="A132" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B132" s="10" t="n">
         <v>28.55</v>
       </c>
-      <c r="C132" s="8" t="n">
+      <c r="C132" s="10" t="n">
         <v>22.02</v>
       </c>
+      <c r="D132" s="11" t="n"/>
+      <c r="E132" s="11" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B133" s="11" t="n">
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B133" s="14" t="n">
         <v>25.98</v>
       </c>
-      <c r="C133" s="11" t="n">
+      <c r="C133" s="14" t="n">
         <v>21.58</v>
       </c>
+      <c r="D133" s="15" t="n"/>
+      <c r="E133" s="15" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B134" s="8" t="n">
+      <c r="A134" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B134" s="10" t="n">
         <v>32.92</v>
       </c>
-      <c r="C134" s="8" t="n">
+      <c r="C134" s="10" t="n">
         <v>22.56</v>
       </c>
-    </row>
-    <row r="136">
+      <c r="D134" s="11" t="n"/>
+      <c r="E134" s="11" t="n"/>
+    </row>
+    <row r="136" ht="30" customHeight="1">
       <c r="A136" s="5" t="inlineStr">
         <is>
           <t>Rakovene</t>
@@ -1957,51 +2397,67 @@
       </c>
       <c r="B136" s="6" t="n"/>
       <c r="C136" s="6" t="n"/>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E136" s="8" t="inlineStr">
+        <is>
+          <t>Pochven only</t>
+        </is>
+      </c>
     </row>
     <row r="137">
-      <c r="A137" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B137" s="8" t="n">
+      <c r="A137" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B137" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="C137" s="8" t="n">
+      <c r="C137" s="10" t="n">
         <v>5000</v>
       </c>
+      <c r="D137" s="11" t="n"/>
+      <c r="E137" s="11" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B138" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C138" s="11" t="n">
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C138" s="14" t="n">
         <v>5000</v>
       </c>
+      <c r="D138" s="15" t="n"/>
+      <c r="E138" s="15" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B139" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C139" s="8" t="n">
+      <c r="A139" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B139" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C139" s="10" t="n">
         <v>5500</v>
       </c>
-    </row>
-    <row r="141">
+      <c r="D139" s="11" t="n"/>
+      <c r="E139" s="11" t="n"/>
+    </row>
+    <row r="141" ht="30" customHeight="1">
       <c r="A141" s="5" t="inlineStr">
         <is>
           <t>Scordite</t>
@@ -2009,47 +2465,63 @@
       </c>
       <c r="B141" s="6" t="n"/>
       <c r="C141" s="6" t="n"/>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>0.15 m³</t>
+        </is>
+      </c>
+      <c r="E141" s="8" t="inlineStr">
+        <is>
+          <t>High-sec / Low-sec / Wormholes</t>
+        </is>
+      </c>
     </row>
     <row r="142">
-      <c r="A142" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="n">
+      <c r="A142" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B142" s="10" t="n">
         <v>21.54</v>
       </c>
-      <c r="C142" s="8" t="n">
+      <c r="C142" s="10" t="n">
         <v>14.78</v>
       </c>
+      <c r="D142" s="11" t="n"/>
+      <c r="E142" s="11" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B143" s="11" t="n">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B143" s="14" t="n">
         <v>21.71</v>
       </c>
-      <c r="C143" s="11" t="n">
+      <c r="C143" s="14" t="n">
         <v>16.72</v>
       </c>
+      <c r="D143" s="15" t="n"/>
+      <c r="E143" s="15" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B144" s="8" t="n">
+      <c r="A144" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B144" s="10" t="n">
         <v>23.69</v>
       </c>
-      <c r="C144" s="8" t="n">
+      <c r="C144" s="10" t="n">
         <v>15.94</v>
       </c>
-    </row>
-    <row r="146">
+      <c r="D144" s="11" t="n"/>
+      <c r="E144" s="11" t="n"/>
+    </row>
+    <row r="146" ht="30" customHeight="1">
       <c r="A146" s="5" t="inlineStr">
         <is>
           <t>Spodumain</t>
@@ -2057,51 +2529,67 @@
       </c>
       <c r="B146" s="6" t="n"/>
       <c r="C146" s="6" t="n"/>
+      <c r="D146" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E146" s="8" t="inlineStr">
+        <is>
+          <t>Pochven</t>
+        </is>
+      </c>
     </row>
     <row r="147">
-      <c r="A147" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B147" s="8" t="n">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B147" s="10" t="n">
         <v>15802.86</v>
       </c>
-      <c r="C147" s="8" t="n">
+      <c r="C147" s="10" t="n">
         <v>7967</v>
       </c>
+      <c r="D147" s="11" t="n"/>
+      <c r="E147" s="11" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B148" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C148" s="11" t="n">
+      <c r="A148" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="n">
         <v>5562.6</v>
       </c>
+      <c r="D148" s="15" t="n"/>
+      <c r="E148" s="15" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B149" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C149" s="8" t="n">
+      <c r="A149" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B149" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C149" s="10" t="n">
         <v>4972.5</v>
       </c>
-    </row>
-    <row r="151">
+      <c r="D149" s="11" t="n"/>
+      <c r="E149" s="11" t="n"/>
+    </row>
+    <row r="151" ht="30" customHeight="1">
       <c r="A151" s="5" t="inlineStr">
         <is>
           <t>Talassonite</t>
@@ -2109,49 +2597,65 @@
       </c>
       <c r="B151" s="6" t="n"/>
       <c r="C151" s="6" t="n"/>
+      <c r="D151" s="7" t="inlineStr">
+        <is>
+          <t>16 m³</t>
+        </is>
+      </c>
+      <c r="E151" s="8" t="inlineStr">
+        <is>
+          <t>Pochven only</t>
+        </is>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B152" s="8" t="n">
+      <c r="A152" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B152" s="10" t="n">
         <v>13430</v>
       </c>
-      <c r="C152" s="8" t="n">
+      <c r="C152" s="10" t="n">
         <v>4759</v>
       </c>
+      <c r="D152" s="11" t="n"/>
+      <c r="E152" s="11" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B153" s="11" t="n">
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="n">
         <v>15000</v>
       </c>
-      <c r="C153" s="11" t="n">
+      <c r="C153" s="14" t="n">
         <v>5140</v>
       </c>
+      <c r="D153" s="15" t="n"/>
+      <c r="E153" s="15" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B154" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C154" s="8" t="n">
+      <c r="A154" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B154" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C154" s="10" t="n">
         <v>5055.5</v>
       </c>
-    </row>
-    <row r="156">
+      <c r="D154" s="11" t="n"/>
+      <c r="E154" s="11" t="n"/>
+    </row>
+    <row r="156" ht="30" customHeight="1">
       <c r="A156" s="5" t="inlineStr">
         <is>
           <t>Tyranite</t>
@@ -2159,55 +2663,71 @@
       </c>
       <c r="B156" s="6" t="n"/>
       <c r="C156" s="6" t="n"/>
+      <c r="D156" s="7" t="inlineStr">
+        <is>
+          <t>0.6 m³</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>Special/limited resource; not a normal security-space belt ore</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B157" s="8" t="n">
+      <c r="A157" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B157" s="10" t="n">
         <v>200</v>
       </c>
-      <c r="C157" s="8" t="n">
+      <c r="C157" s="10" t="n">
         <v>4.51</v>
       </c>
+      <c r="D157" s="11" t="n"/>
+      <c r="E157" s="11" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B158" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C158" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
+      <c r="A158" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B158" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C158" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D158" s="15" t="n"/>
+      <c r="E158" s="15" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B159" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C159" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
+      <c r="A159" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B159" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C159" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="D159" s="11" t="n"/>
+      <c r="E159" s="11" t="n"/>
+    </row>
+    <row r="161" ht="30" customHeight="1">
       <c r="A161" s="5" t="inlineStr">
         <is>
           <t>Ueganite</t>
@@ -2215,49 +2735,65 @@
       </c>
       <c r="B161" s="6" t="n"/>
       <c r="C161" s="6" t="n"/>
+      <c r="D161" s="7" t="inlineStr">
+        <is>
+          <t>5 m³</t>
+        </is>
+      </c>
+      <c r="E161" s="8" t="inlineStr">
+        <is>
+          <t>Null-sec Sov-Hub anomalies</t>
+        </is>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="n">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B162" s="10" t="n">
         <v>4500</v>
       </c>
-      <c r="C162" s="8" t="n">
+      <c r="C162" s="10" t="n">
         <v>503.25</v>
       </c>
+      <c r="D162" s="11" t="n"/>
+      <c r="E162" s="11" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B163" s="11" t="n">
+      <c r="A163" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B163" s="14" t="n">
         <v>4512</v>
       </c>
-      <c r="C163" s="11" t="n">
+      <c r="C163" s="14" t="n">
         <v>513</v>
       </c>
+      <c r="D163" s="15" t="n"/>
+      <c r="E163" s="15" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B164" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C164" s="8" t="n">
+      <c r="A164" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B164" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C164" s="10" t="n">
         <v>552.05</v>
       </c>
-    </row>
-    <row r="166">
+      <c r="D164" s="11" t="n"/>
+      <c r="E164" s="11" t="n"/>
+    </row>
+    <row r="166" ht="30" customHeight="1">
       <c r="A166" s="5" t="inlineStr">
         <is>
           <t>Veldspar</t>
@@ -2265,47 +2801,63 @@
       </c>
       <c r="B166" s="6" t="n"/>
       <c r="C166" s="6" t="n"/>
+      <c r="D166" s="7" t="inlineStr">
+        <is>
+          <t>0.1 m³</t>
+        </is>
+      </c>
+      <c r="E166" s="8" t="inlineStr">
+        <is>
+          <t>High-sec / special starter &amp; managed belts; Low-sec/W-space exceptions</t>
+        </is>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B167" s="8" t="n">
+      <c r="A167" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B167" s="10" t="n">
         <v>14.51</v>
       </c>
-      <c r="C167" s="8" t="n">
+      <c r="C167" s="10" t="n">
         <v>10.14</v>
       </c>
+      <c r="D167" s="11" t="n"/>
+      <c r="E167" s="11" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B168" s="11" t="n">
+      <c r="A168" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B168" s="14" t="n">
         <v>12.99</v>
       </c>
-      <c r="C168" s="11" t="n">
+      <c r="C168" s="14" t="n">
         <v>10.65</v>
       </c>
+      <c r="D168" s="15" t="n"/>
+      <c r="E168" s="15" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B169" s="8" t="n">
+      <c r="A169" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B169" s="10" t="n">
         <v>13.53</v>
       </c>
-      <c r="C169" s="8" t="n">
+      <c r="C169" s="10" t="n">
         <v>10.44</v>
       </c>
-    </row>
-    <row r="171">
+      <c r="D169" s="11" t="n"/>
+      <c r="E169" s="11" t="n"/>
+    </row>
+    <row r="171" ht="30" customHeight="1">
       <c r="A171" s="5" t="inlineStr">
         <is>
           <t>Ytirium</t>
@@ -2313,49 +2865,65 @@
       </c>
       <c r="B171" s="6" t="n"/>
       <c r="C171" s="6" t="n"/>
+      <c r="D171" s="7" t="inlineStr">
+        <is>
+          <t>0.6 m³</t>
+        </is>
+      </c>
+      <c r="E171" s="8" t="inlineStr">
+        <is>
+          <t>0.5 High/Low border, Null-sec &amp; Wormhole A0 systems</t>
+        </is>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="7" t="inlineStr">
-        <is>
-          <t>Grade I</t>
-        </is>
-      </c>
-      <c r="B172" s="8" t="n">
+      <c r="A172" s="9" t="inlineStr">
+        <is>
+          <t>Grade I</t>
+        </is>
+      </c>
+      <c r="B172" s="10" t="n">
         <v>331.17</v>
       </c>
-      <c r="C172" s="8" t="n">
+      <c r="C172" s="10" t="n">
         <v>249.78</v>
       </c>
+      <c r="D172" s="11" t="n"/>
+      <c r="E172" s="11" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="9" t="inlineStr">
-        <is>
-          <t>Grade II</t>
-        </is>
-      </c>
-      <c r="B173" s="10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C173" s="11" t="n">
+      <c r="A173" s="12" t="inlineStr">
+        <is>
+          <t>Grade II</t>
+        </is>
+      </c>
+      <c r="B173" s="13" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C173" s="14" t="n">
         <v>10000</v>
       </c>
+      <c r="D173" s="15" t="n"/>
+      <c r="E173" s="15" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="7" t="inlineStr">
-        <is>
-          <t>Grade III</t>
-        </is>
-      </c>
-      <c r="B174" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="C174" s="8" t="n">
+      <c r="A174" s="9" t="inlineStr">
+        <is>
+          <t>Grade III</t>
+        </is>
+      </c>
+      <c r="B174" s="16" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C174" s="10" t="n">
         <v>10000</v>
       </c>
+      <c r="D174" s="11" t="n"/>
+      <c r="E174" s="11" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -2363,12 +2931,11 @@
     <mergeCell ref="A66:C66"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A56:C56"/>
-    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A101:C101"/>
     <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A101:C101"/>
     <mergeCell ref="A136:C136"/>
     <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A86:C86"/>
     <mergeCell ref="A76:C76"/>
     <mergeCell ref="A71:C71"/>
@@ -2383,15 +2950,16 @@
     <mergeCell ref="A96:C96"/>
     <mergeCell ref="A156:C156"/>
     <mergeCell ref="A171:C171"/>
+    <mergeCell ref="A3:E3"/>
     <mergeCell ref="A121:C121"/>
     <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A2:E2"/>
     <mergeCell ref="A111:C111"/>
     <mergeCell ref="A31:C31"/>
     <mergeCell ref="A166:C166"/>
     <mergeCell ref="A51:C51"/>
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A61:C61"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A146:C146"/>
